--- a/src/advising/Module_catalogue.xlsx
+++ b/src/advising/Module_catalogue.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universityofstandrews907-my.sharepoint.com/personal/dwrj1_st-andrews_ac_uk/Documents/DoT/Advising/Advising-tool/StA_Advising/src/advising/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universityofstandrews907-my.sharepoint.com/personal/hw233_st-andrews_ac_uk/Documents/Service STAR/School Service/DoT/StA_Advising/src/advising/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{512B0E99-D0D4-904E-9A76-C0B28B78645E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A35AD11E-3F4C-3242-9ADE-F9D7EBF4B636}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{512B0E99-D0D4-904E-9A76-C0B28B78645E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32C05BCD-C201-4DCE-A4B9-4D33C22A6196}"/>
   <bookViews>
-    <workbookView xWindow="1760" yWindow="800" windowWidth="29400" windowHeight="17160" xr2:uid="{4F9A127D-94E5-E147-ADFA-9B9D4F5F7BAB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4F9A127D-94E5-E147-ADFA-9B9D4F5F7BAB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="324">
   <si>
     <t>Module code</t>
   </si>
@@ -1008,6 +1008,9 @@
   </si>
   <si>
     <t>2027/2028</t>
+  </si>
+  <si>
+    <t>2028/2029</t>
   </si>
 </sst>
 </file>
@@ -1391,22 +1394,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{692125B0-B9FD-1C45-BA4C-1792B9B50D49}">
   <dimension ref="A1:J106"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.83203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="70.83203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.83203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.33203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="59.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15.796875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="70.796875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.796875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.296875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="59.69921875" style="1" customWidth="1"/>
     <col min="6" max="6" width="19" style="1" customWidth="1"/>
     <col min="7" max="7" width="138" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="69.1640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="69.19921875" style="1" customWidth="1"/>
     <col min="9" max="9" width="35" style="1" customWidth="1"/>
     <col min="10" max="10" width="22.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="10.83203125" style="1"/>
+    <col min="11" max="16384" width="10.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="2" customFormat="1" ht="40" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="2" customFormat="1" ht="36" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1438,7 +1441,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>271</v>
       </c>
@@ -1469,7 +1472,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>274</v>
       </c>
@@ -1500,7 +1503,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="4" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>268</v>
       </c>
@@ -1531,7 +1534,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="5" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>297</v>
       </c>
@@ -1561,7 +1564,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="6" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -1591,7 +1594,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -1622,7 +1625,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>309</v>
       </c>
@@ -1653,7 +1656,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>311</v>
       </c>
@@ -1684,7 +1687,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -1714,7 +1717,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
@@ -1744,7 +1747,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>17</v>
       </c>
@@ -1774,7 +1777,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -1804,7 +1807,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
@@ -1834,7 +1837,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>23</v>
       </c>
@@ -1864,7 +1867,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>26</v>
       </c>
@@ -1894,7 +1897,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>29</v>
       </c>
@@ -1924,7 +1927,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>32</v>
       </c>
@@ -1954,7 +1957,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>34</v>
       </c>
@@ -1987,7 +1990,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
@@ -2014,7 +2017,7 @@
         <v>Temp withdrawal</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>40</v>
       </c>
@@ -2044,7 +2047,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>42</v>
       </c>
@@ -2074,7 +2077,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>44</v>
       </c>
@@ -2104,7 +2107,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>47</v>
       </c>
@@ -2134,7 +2137,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>49</v>
       </c>
@@ -2164,7 +2167,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>51</v>
       </c>
@@ -2197,7 +2200,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>55</v>
       </c>
@@ -2227,7 +2230,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>57</v>
       </c>
@@ -2257,7 +2260,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>59</v>
       </c>
@@ -2284,7 +2287,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>62</v>
       </c>
@@ -2314,7 +2317,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>64</v>
       </c>
@@ -2344,7 +2347,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>66</v>
       </c>
@@ -2374,7 +2377,7 @@
         <v>Alternates (2026/27)</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>68</v>
       </c>
@@ -2407,7 +2410,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>74</v>
       </c>
@@ -2437,7 +2440,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>78</v>
       </c>
@@ -2470,7 +2473,7 @@
         <v>Alternates (2027/28)</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>82</v>
       </c>
@@ -2503,7 +2506,7 @@
         <v>Alternates (2026/27)</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>87</v>
       </c>
@@ -2533,7 +2536,7 @@
         <v>Alternates (2027/28)</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>89</v>
       </c>
@@ -2563,7 +2566,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>91</v>
       </c>
@@ -2593,7 +2596,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>93</v>
       </c>
@@ -2623,7 +2626,7 @@
         <v>Alternates (2026/27)</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>95</v>
       </c>
@@ -2656,7 +2659,7 @@
         <v>Alternates (2026/27)</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>99</v>
       </c>
@@ -2686,7 +2689,7 @@
         <v>Alternates (2027/28)</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>102</v>
       </c>
@@ -2716,7 +2719,7 @@
         <v>Alternates (2026/27)</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>104</v>
       </c>
@@ -2746,7 +2749,7 @@
         <v>Alternates (2026/27)</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>107</v>
       </c>
@@ -2776,7 +2779,7 @@
         <v>Alternates (2027/28)</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>110</v>
       </c>
@@ -2806,7 +2809,7 @@
         <v>Alternates (2027/28)</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>113</v>
       </c>
@@ -2836,7 +2839,7 @@
         <v>Alternates (2027/28)</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>115</v>
       </c>
@@ -2866,7 +2869,7 @@
         <v>Alternates (2026/27)</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>117</v>
       </c>
@@ -2896,7 +2899,7 @@
         <v>Alternates (2027/28)</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>119</v>
       </c>
@@ -2926,7 +2929,7 @@
         <v>Temp withdrawal</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>122</v>
       </c>
@@ -2959,7 +2962,7 @@
         <v>Alternates (2026/27)</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>126</v>
       </c>
@@ -2989,7 +2992,7 @@
         <v>Temp withdrawal</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>129</v>
       </c>
@@ -3019,7 +3022,7 @@
         <v>Temp withdrawal</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>133</v>
       </c>
@@ -3049,7 +3052,7 @@
         <v>Alternates (2027/28)</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>135</v>
       </c>
@@ -3079,7 +3082,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>137</v>
       </c>
@@ -3112,7 +3115,7 @@
         <v>Alternates (2026/27)</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>141</v>
       </c>
@@ -3142,7 +3145,7 @@
         <v>Alternates (2027/28)</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>277</v>
       </c>
@@ -3150,7 +3153,7 @@
         <v>278</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>128</v>
+        <v>323</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>11</v>
@@ -3172,7 +3175,7 @@
         <v>Alternates (2026/27)</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>292</v>
       </c>
@@ -3202,7 +3205,7 @@
         <v>Alternates (2027/28)</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>291</v>
       </c>
@@ -3232,7 +3235,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>144</v>
       </c>
@@ -3259,7 +3262,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>148</v>
       </c>
@@ -3283,7 +3286,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>150</v>
       </c>
@@ -3316,7 +3319,7 @@
         <v>Alternates (2027/28)</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>153</v>
       </c>
@@ -3346,7 +3349,7 @@
         <v>Alternates (2026/27)</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
         <v>155</v>
       </c>
@@ -3376,7 +3379,7 @@
         <v>Temp withdrawal</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
         <v>158</v>
       </c>
@@ -3403,7 +3406,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
         <v>160</v>
       </c>
@@ -3430,7 +3433,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>162</v>
       </c>
@@ -3454,7 +3457,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>164</v>
       </c>
@@ -3478,7 +3481,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>166</v>
       </c>
@@ -3505,7 +3508,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>168</v>
       </c>
@@ -3529,7 +3532,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>170</v>
       </c>
@@ -3559,7 +3562,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
         <v>172</v>
       </c>
@@ -3583,7 +3586,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
         <v>174</v>
       </c>
@@ -3616,7 +3619,7 @@
         <v>Alternates (2026/27)</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
         <v>177</v>
       </c>
@@ -3646,7 +3649,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
         <v>180</v>
       </c>
@@ -3679,7 +3682,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
         <v>183</v>
       </c>
@@ -3712,7 +3715,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
         <v>188</v>
       </c>
@@ -3745,7 +3748,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
         <v>193</v>
       </c>
@@ -3778,7 +3781,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
         <v>195</v>
       </c>
@@ -3811,7 +3814,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
         <v>199</v>
       </c>
@@ -3841,7 +3844,7 @@
         <v>Alternates (2027/28)</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
         <v>201</v>
       </c>
@@ -3871,7 +3874,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>204</v>
       </c>
@@ -3901,7 +3904,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
         <v>206</v>
       </c>
@@ -3934,7 +3937,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
         <v>209</v>
       </c>
@@ -3964,7 +3967,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
         <v>211</v>
       </c>
@@ -3997,7 +4000,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
         <v>214</v>
       </c>
@@ -4030,7 +4033,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
         <v>217</v>
       </c>
@@ -4063,7 +4066,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
         <v>220</v>
       </c>
@@ -4093,7 +4096,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
         <v>222</v>
       </c>
@@ -4123,7 +4126,7 @@
         <v>Alternates (2027/28)</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
         <v>223</v>
       </c>
@@ -4153,7 +4156,7 @@
         <v>Alternates (2026/27)</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
         <v>225</v>
       </c>
@@ -4186,7 +4189,7 @@
         <v>Alternates (2027/28)</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
         <v>229</v>
       </c>
@@ -4216,7 +4219,7 @@
         <v>Alternates (2027/28)</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
         <v>232</v>
       </c>
@@ -4249,7 +4252,7 @@
         <v>Alternates (2027/28)</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
         <v>237</v>
       </c>
@@ -4282,7 +4285,7 @@
         <v>Alternates (2027/28)</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
         <v>240</v>
       </c>
@@ -4315,7 +4318,7 @@
         <v>Runs every year</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
         <v>243</v>
       </c>
@@ -4345,7 +4348,7 @@
         <v>Alternates (2026/27)</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
         <v>246</v>
       </c>
@@ -4378,7 +4381,7 @@
         <v>Alternates (2026/27)</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
         <v>250</v>
       </c>
@@ -4408,7 +4411,7 @@
         <v>Temp withdrawal</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
         <v>252</v>
       </c>
@@ -4438,7 +4441,7 @@
         <v>Alternates (2026/27)</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
         <v>255</v>
       </c>
@@ -4471,7 +4474,7 @@
         <v>Alternates (2026/27)</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A102" s="5" t="s">
         <v>305</v>
       </c>
@@ -4501,7 +4504,7 @@
         <v>Alternates (2026/27)</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A103" s="5" t="s">
         <v>307</v>
       </c>
@@ -4531,7 +4534,7 @@
         <v>Alternates (2027/28)</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A104" s="1" t="s">
         <v>259</v>
       </c>
@@ -4564,7 +4567,7 @@
         <v>Alternates (2026/27)</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
         <v>262</v>
       </c>
@@ -4597,7 +4600,7 @@
         <v>Alternates (2027/28)</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
         <v>266</v>
       </c>
